--- a/강의 자료/테이블 명세서.xlsx
+++ b/강의 자료/테이블 명세서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\211-11\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevPrograms\workspace\강의 자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7084AD-906F-43BC-B4D0-3953E3DB240E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD37173-AF07-4F89-8F1B-ADFB6EF3010C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{802E7722-B099-FB4F-89D0-B5B50B7F50C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{802E7722-B099-FB4F-89D0-B5B50B7F50C7}"/>
   </bookViews>
   <sheets>
     <sheet name="영화" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="266">
   <si>
     <t>컬럼명</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1064,6 +1064,30 @@
   </si>
   <si>
     <t>MK-연월일(8자리)-일련번호(6자리)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEL_YN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>삭제 여부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 CHAR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"N"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N: 삭제 안됨, Y: 삭제 완료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.31 최미서 수정(2026.08.31일 데이터 삭제 회의에 따른 추가)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1694,7 +1718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988B250B-609D-0E4C-BE90-25AD323941FD}">
-  <dimension ref="B1:L23"/>
+  <dimension ref="B1:M23"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="2" customWidth="1"/>
@@ -1708,7 +1732,8 @@
     <col min="10" max="10" width="18.33203125" style="4" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" style="4" customWidth="1"/>
     <col min="12" max="12" width="26.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.6640625" style="2"/>
+    <col min="13" max="13" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="10.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="24.95" customHeight="1">
@@ -1747,7 +1772,9 @@
       <c r="K2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="7"/>
+      <c r="L2" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="3" spans="2:12" ht="24.95" customHeight="1">
       <c r="B3" s="23"/>
@@ -1770,7 +1797,9 @@
       <c r="K3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="7"/>
+      <c r="L3" s="7">
+        <v>8.31</v>
+      </c>
     </row>
     <row r="4" spans="2:12" ht="24.95" customHeight="1" thickBot="1">
       <c r="B4" s="6" t="s">
@@ -2093,7 +2122,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="2:12" ht="24.95" customHeight="1">
+    <row r="17" spans="2:13" ht="24.95" customHeight="1">
       <c r="B17" s="3">
         <v>11</v>
       </c>
@@ -2118,7 +2147,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="2:12" ht="24.95" customHeight="1">
+    <row r="18" spans="2:13" ht="24.95" customHeight="1">
       <c r="B18" s="3">
         <v>12</v>
       </c>
@@ -2143,7 +2172,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="2:12" ht="24.95" customHeight="1">
+    <row r="19" spans="2:13" ht="24.95" customHeight="1">
       <c r="B19" s="3">
         <v>13</v>
       </c>
@@ -2168,7 +2197,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="2:12" ht="24.95" customHeight="1">
+    <row r="20" spans="2:13" ht="24.95" customHeight="1">
       <c r="B20" s="3">
         <v>14</v>
       </c>
@@ -2193,7 +2222,7 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="2:12" ht="24.95" customHeight="1">
+    <row r="21" spans="2:13" ht="24.95" customHeight="1">
       <c r="B21" s="3">
         <v>15</v>
       </c>
@@ -2220,7 +2249,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="24.95" customHeight="1">
+    <row r="22" spans="2:13" ht="24.95" customHeight="1">
       <c r="B22" s="13">
         <v>16</v>
       </c>
@@ -2247,18 +2276,37 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
+    <row r="23" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B23" s="3">
+        <v>17</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>265</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
